--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.2%</t>
+          <t>-562.3%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.48068891723439</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.3983259583189</v>
+        <v>3.398325958318901</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.006110057449762</v>
+        <v>-4.007447249954452</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.324258031802257</v>
+        <v>1.323723154800381</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4787331399567458</v>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.9%</t>
+          <t>780.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.3%</t>
+          <t>-574.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-39.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-243.8%</t>
+          <t>-248.7%</t>
         </is>
       </c>
     </row>
@@ -46102,10 +46102,10 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.007447249954452</v>
+        <v>-4.127618830216249</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.323723154800381</v>
+        <v>1.275654522695662</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4787331399567458</v>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>139.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.6%</t>
+          <t>788.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.3%</t>
+          <t>-546.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.6%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-248.7%</t>
+          <t>-237.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.9%</t>
+          <t>-161.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.9%</t>
+          <t>-262.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-176.6%</t>
         </is>
       </c>
     </row>
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.9394593044078</v>
+        <v>-11.78278555302748</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.596516593565497</v>
+        <v>-1.533847093013367</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.589611495412947</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9713647329063866</v>
+        <v>1.025856655263603</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.65555057347905</v>
+        <v>-11.49887682209873</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.477219396955361</v>
+        <v>-1.414549896403232</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.589611495412947</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9770984371450231</v>
+        <v>1.03159035950224</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4085633232861</v>
+        <v>-11.25188957190578</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.388161759272045</v>
+        <v>-1.325492258719916</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.342624245219995</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.115553524866929</v>
+        <v>1.170045447224146</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14472645608203</v>
+        <v>-10.98805270470171</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292510493703325</v>
+        <v>-1.229840993151196</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.342624245219995</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.105670043554022</v>
+        <v>1.160161965911238</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87748465521363</v>
+        <v>-10.72081090383331</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.187448333855339</v>
+        <v>-1.12477883330321</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.342624245219995</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.103835483054648</v>
+        <v>1.158327405411864</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60167549181315</v>
+        <v>-10.44500174043283</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.077424983468606</v>
+        <v>-1.014755482916477</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.344424807536623</v>
+        <v>-3.253604936941262</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156946753048427</v>
+        <v>1.211438675405644</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57772195083719</v>
+        <v>-10.42104819945687</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.067175060932729</v>
+        <v>-1.0045055603806</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.320471266560665</v>
+        <v>-3.229651395965304</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171987383779495</v>
+        <v>1.226479306136712</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31366201251439</v>
+        <v>-10.15698826113407</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9748114017653631</v>
+        <v>-0.9121419012132339</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.965591457642508</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.317163030611421</v>
+        <v>1.371654952968637</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.606582389009557</v>
+        <v>-9.449908637629234</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6947665860237291</v>
+        <v>-0.6320970854715999</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.965591457642508</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.31437599695112</v>
+        <v>1.368867919308336</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.566398090643366</v>
+        <v>-9.409724339263043</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6783492427894116</v>
+        <v>-0.6156797422372824</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.016227029871678</v>
+        <v>-2.925407159276317</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338830199858676</v>
+        <v>1.393322122215892</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.486328295105562</v>
+        <v>-9.329654543725239</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6469545033535327</v>
+        <v>-0.5842850028014035</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.936157234333874</v>
+        <v>-2.845337363738513</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.386238898402115</v>
+        <v>1.440730820759332</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.252847072875962</v>
+        <v>-9.096173321495641</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5456375856238407</v>
+        <v>-0.482968085071712</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.702676012104276</v>
+        <v>-2.611856141508915</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.534252060577727</v>
+        <v>1.588743982934943</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.073138542732089</v>
+        <v>-8.916464791351768</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4766463838792503</v>
+        <v>-0.413976883327122</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64550450794158</v>
+        <v>-2.554684637346219</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.565662752762385</v>
+        <v>1.620154675119601</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.940863069101201</v>
+        <v>-8.78418931772088</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4283687076798683</v>
+        <v>-0.3656992071277401</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.513229034310693</v>
+        <v>-2.422409163715332</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.640395523687944</v>
+        <v>1.69488744604516</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.750263394428048</v>
+        <v>-8.593589643047727</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3493137771229704</v>
+        <v>-0.2866442765708417</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.23180948904218</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.757570389179472</v>
+        <v>1.812062311536689</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.501263595744467</v>
+        <v>-8.344589844364146</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2368075164258792</v>
+        <v>-0.1741380158737509</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.23180948904218</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.770476730403131</v>
+        <v>1.824968652760347</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.606853585517571</v>
+        <v>-8.45017983413725</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4070194419343398</v>
+        <v>-0.3443499413822111</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.337399478815284</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.579146806940049</v>
+        <v>1.633638729297266</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.625588487636168</v>
+        <v>-8.468914736255847</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3659690609046922</v>
+        <v>-0.3032995603525634</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.337399478815284</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.627691148817136</v>
+        <v>1.682183071174352</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.477648446228569</v>
+        <v>-8.320974694848248</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.42667196702982</v>
+        <v>-0.3640024664776913</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.407898433502087</v>
+        <v>-2.317078562906727</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.520004775674103</v>
+        <v>1.57449669803132</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.350756039793499</v>
+        <v>-8.194082288413178</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3846289907092699</v>
+        <v>-0.3219594901571416</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.587426233281667</v>
+        <v>1.641918155638883</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.307207633022808</v>
+        <v>-8.150533881642486</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3741702400960865</v>
+        <v>-0.3115007395439582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.580465621186574</v>
+        <v>1.63495754354379</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.065059239568949</v>
+        <v>-7.908385488188628</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2628485283334001</v>
+        <v>-0.2001790277812718</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.594927975567717</v>
+        <v>1.649419897924933</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.001829867800602</v>
+        <v>-7.84515611642028</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2430246591668661</v>
+        <v>-0.1803551586147374</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.589460096026912</v>
+        <v>1.643952018384128</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.815342175423596</v>
+        <v>-7.658668424043274</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1709314882054866</v>
+        <v>-0.1082619876533584</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.094518334690011</v>
+        <v>-2.003698464094651</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.698850805463692</v>
+        <v>1.753342727820909</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.794192976520153</v>
+        <v>-7.637519225139831</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1547708304067843</v>
+        <v>-0.09210132985465558</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.073369135786568</v>
+        <v>-1.982549265191207</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.719241303043084</v>
+        <v>1.7737332254003</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.550427534536708</v>
+        <v>-7.393753783156386</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.06148394526635581</v>
+        <v>0.00118555528577291</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.073369135786568</v>
+        <v>-1.982549265191207</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.715022011390134</v>
+        <v>1.769513933747351</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.286399467343448</v>
+        <v>-7.129725715963126</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04625159553096436</v>
+        <v>0.1089210960830931</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.780683866375254</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.838265564599722</v>
+        <v>1.892757486956939</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.036549073394373</v>
+        <v>-6.879875322014051</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1389338280942964</v>
+        <v>0.2016033286464247</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.780683866375254</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.831007639583424</v>
+        <v>1.885499561940641</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.732981584390394</v>
+        <v>-6.576307833010072</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2639599472165366</v>
+        <v>0.3266294477686653</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.780683866375254</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.834606763104073</v>
+        <v>1.88909868546129</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.65950167553838</v>
+        <v>-6.502827924158058</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.306679416811896</v>
+        <v>0.3693489173640243</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.7980238281186</v>
+        <v>-1.707203957523239</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.892022214469836</v>
+        <v>1.946514136827052</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.434468675869558</v>
+        <v>-6.277794924489235</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3957130942957221</v>
+        <v>0.4583825948478504</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.572990828449777</v>
+        <v>-1.482170957854416</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.026062491887426</v>
+        <v>2.080554414244643</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.219834298233151</v>
+        <v>-6.063160546852829</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4862616464046021</v>
+        <v>0.5489311469567304</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.35835645081337</v>
+        <v>-1.26753658021801</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.159537919523587</v>
+        <v>2.214029841880804</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.953233941258799</v>
+        <v>-5.796560189878477</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5740960479781387</v>
+        <v>0.636765548530267</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.35835645081337</v>
+        <v>-1.26753658021801</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.140732178307383</v>
+        <v>2.1952241006646</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.712803444453939</v>
+        <v>-5.556129693073617</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6720113233249601</v>
+        <v>0.7346808238770883</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.11792595400851</v>
+        <v>-1.027106083413149</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.286733553015177</v>
+        <v>2.341225475372393</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.470012636804493</v>
+        <v>-5.313338885424171</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7730569602195585</v>
+        <v>0.8357264607716868</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.11792595400851</v>
+        <v>-1.027106083413149</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.290662866849997</v>
+        <v>2.345154789207213</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.230407545197404</v>
+        <v>-5.073733793817082</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8695775807797341</v>
+        <v>0.9322470813318624</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.050878006340016</v>
+        <v>-0.9600581357446548</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.331570219368434</v>
+        <v>2.38606214172565</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.987751956774241</v>
+        <v>-4.831078205393919</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.963637887368993</v>
+        <v>1.026307387921122</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.050878006340016</v>
+        <v>-0.9600581357446548</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.328568290588427</v>
+        <v>2.383060212945644</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.76773115873723</v>
+        <v>-4.611057407356908</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.053225243594411</v>
+        <v>1.11589474414654</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9096581612720354</v>
+        <v>-0.8188382906766746</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.414879234639829</v>
+        <v>2.469371156997046</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.568482528832421</v>
+        <v>-4.411808777452099</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.148818878358158</v>
+        <v>1.211488378910287</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9096581612720354</v>
+        <v>-0.8188382906766746</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.430773417441653</v>
+        <v>2.485265339798869</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.408967425313051</v>
+        <v>-4.252293673932729</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.213770764206208</v>
+        <v>1.276440264758337</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7501430577526654</v>
+        <v>-0.6593231871573046</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.527628323993576</v>
+        <v>2.582120246350793</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.264295280213314</v>
+        <v>-4.107621528832992</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.281727724807543</v>
+        <v>1.344397225359671</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6054709126529281</v>
+        <v>-0.5146510420575672</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.624519713614859</v>
+        <v>2.679011635972075</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.246525821282358</v>
+        <v>-4.089852069902036</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.204175200466647</v>
+        <v>1.266844701018775</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5877014537219725</v>
+        <v>-0.4968815831266116</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.550521081060154</v>
+        <v>2.60501300341737</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.159726323503349</v>
+        <v>-4.003052572123027</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.261295492900817</v>
+        <v>1.323964993452945</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5877014537219725</v>
+        <v>-0.4968815831266116</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.57292157438272</v>
+        <v>2.627413496739937</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.060033708774337</v>
+        <v>-3.903359957394015</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.301244940165833</v>
+        <v>1.363914440717962</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4880088389929607</v>
+        <v>-0.3971889683975999</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.632809544593539</v>
+        <v>2.687301466950756</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.128403895098347</v>
+        <v>-3.971730143718025</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.284903788110932</v>
+        <v>1.34757328866306</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.3879132693613849</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.64938188648997</v>
+        <v>2.703873808847187</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.398325958318901</v>
+        <v>3.834187725245797</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.127618830216249</v>
+        <v>-3.850313714091548</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.275654522695662</v>
+        <v>1.386576569145542</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.3879132693613849</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.639818595121861</v>
+        <v>2.694310517479078</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-36.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.0%</t>
+          <t>138.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.8%</t>
+          <t>780.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-546.6%</t>
+          <t>-574.3%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-39.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-237.6%</t>
+          <t>-248.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-159.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-262.8%</t>
+          <t>-271.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.6%</t>
+          <t>-171.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1937"/>
+  <dimension ref="A1:G1938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78278555302748</v>
+        <v>-11.9394593044078</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.533847093013367</v>
+        <v>-1.596516593565497</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.589611495412947</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.025856655263603</v>
+        <v>0.9713647329063866</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.49887682209873</v>
+        <v>-11.65555057347905</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.414549896403232</v>
+        <v>-1.477219396955361</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.589611495412947</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.03159035950224</v>
+        <v>0.9770984371450231</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.25188957190578</v>
+        <v>-11.4085633232861</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.325492258719916</v>
+        <v>-1.388161759272045</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.342624245219995</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.170045447224146</v>
+        <v>1.115553524866929</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.98805270470171</v>
+        <v>-11.14472645608203</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.229840993151196</v>
+        <v>-1.292510493703325</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.342624245219995</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.160161965911238</v>
+        <v>1.105670043554022</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.72081090383331</v>
+        <v>-10.87748465521363</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.12477883330321</v>
+        <v>-1.187448333855339</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.342624245219995</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.158327405411864</v>
+        <v>1.103835483054648</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.44500174043283</v>
+        <v>-10.60167549181315</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.014755482916477</v>
+        <v>-1.077424983468606</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.253604936941262</v>
+        <v>-3.344424807536623</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.211438675405644</v>
+        <v>1.156946753048427</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.42104819945687</v>
+        <v>-10.57772195083719</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.0045055603806</v>
+        <v>-1.067175060932729</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.229651395965304</v>
+        <v>-3.320471266560665</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.226479306136712</v>
+        <v>1.171987383779495</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.15698826113407</v>
+        <v>-10.31366201251439</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9121419012132339</v>
+        <v>-0.9748114017653631</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.965591457642508</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.371654952968637</v>
+        <v>1.317163030611421</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.449908637629234</v>
+        <v>-9.606582389009557</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6320970854715999</v>
+        <v>-0.6947665860237291</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.965591457642508</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.368867919308336</v>
+        <v>1.31437599695112</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.409724339263043</v>
+        <v>-9.566398090643366</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6156797422372824</v>
+        <v>-0.6783492427894116</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.925407159276317</v>
+        <v>-3.016227029871678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.393322122215892</v>
+        <v>1.338830199858676</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.329654543725239</v>
+        <v>-9.486328295105562</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5842850028014035</v>
+        <v>-0.6469545033535327</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.845337363738513</v>
+        <v>-2.936157234333874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.440730820759332</v>
+        <v>1.386238898402115</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.096173321495641</v>
+        <v>-9.252847072875962</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.482968085071712</v>
+        <v>-0.5456375856238407</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.611856141508915</v>
+        <v>-2.702676012104276</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.588743982934943</v>
+        <v>1.534252060577727</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.916464791351768</v>
+        <v>-9.073138542732089</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.413976883327122</v>
+        <v>-0.4766463838792503</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.554684637346219</v>
+        <v>-2.64550450794158</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.620154675119601</v>
+        <v>1.565662752762385</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.78418931772088</v>
+        <v>-8.940863069101201</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3656992071277401</v>
+        <v>-0.4283687076798683</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.422409163715332</v>
+        <v>-2.513229034310693</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.69488744604516</v>
+        <v>1.640395523687944</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.593589643047727</v>
+        <v>-8.750263394428048</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2866442765708417</v>
+        <v>-0.3493137771229704</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.23180948904218</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.812062311536689</v>
+        <v>1.757570389179472</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.344589844364146</v>
+        <v>-8.501263595744467</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1741380158737509</v>
+        <v>-0.2368075164258792</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.23180948904218</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.824968652760347</v>
+        <v>1.770476730403131</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.45017983413725</v>
+        <v>-8.606853585517571</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3443499413822111</v>
+        <v>-0.4070194419343398</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.337399478815284</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.633638729297266</v>
+        <v>1.579146806940049</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.468914736255847</v>
+        <v>-8.625588487636168</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3032995603525634</v>
+        <v>-0.3659690609046922</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.337399478815284</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.682183071174352</v>
+        <v>1.627691148817136</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.320974694848248</v>
+        <v>-8.477648446228569</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3640024664776913</v>
+        <v>-0.42667196702982</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.317078562906727</v>
+        <v>-2.407898433502087</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.57449669803132</v>
+        <v>1.520004775674103</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.194082288413178</v>
+        <v>-8.350756039793499</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3219594901571416</v>
+        <v>-0.3846289907092699</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.641918155638883</v>
+        <v>1.587426233281667</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.150533881642486</v>
+        <v>-8.307207633022808</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3115007395439582</v>
+        <v>-0.3741702400960865</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.63495754354379</v>
+        <v>1.580465621186574</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.908385488188628</v>
+        <v>-8.065059239568949</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2001790277812718</v>
+        <v>-0.2628485283334001</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.649419897924933</v>
+        <v>1.594927975567717</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.84515611642028</v>
+        <v>-8.001829867800602</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1803551586147374</v>
+        <v>-0.2430246591668661</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.643952018384128</v>
+        <v>1.589460096026912</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.658668424043274</v>
+        <v>-7.815342175423596</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1082619876533584</v>
+        <v>-0.1709314882054866</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.003698464094651</v>
+        <v>-2.094518334690011</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.753342727820909</v>
+        <v>1.698850805463692</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.637519225139831</v>
+        <v>-7.794192976520153</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.09210132985465558</v>
+        <v>-0.1547708304067843</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.982549265191207</v>
+        <v>-2.073369135786568</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.7737332254003</v>
+        <v>1.719241303043084</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.393753783156386</v>
+        <v>-7.550427534536708</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.00118555528577291</v>
+        <v>-0.06148394526635581</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.982549265191207</v>
+        <v>-2.073369135786568</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.769513933747351</v>
+        <v>1.715022011390134</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.129725715963126</v>
+        <v>-7.286399467343448</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1089210960830931</v>
+        <v>0.04625159553096436</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.780683866375254</v>
+        <v>-1.871503736970614</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.892757486956939</v>
+        <v>1.838265564599722</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.879875322014051</v>
+        <v>-7.036549073394373</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2016033286464247</v>
+        <v>0.1389338280942964</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.780683866375254</v>
+        <v>-1.871503736970614</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.885499561940641</v>
+        <v>1.831007639583424</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.576307833010072</v>
+        <v>-6.732981584390394</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3266294477686653</v>
+        <v>0.2639599472165366</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.780683866375254</v>
+        <v>-1.871503736970614</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.88909868546129</v>
+        <v>1.834606763104073</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.502827924158058</v>
+        <v>-6.65950167553838</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3693489173640243</v>
+        <v>0.306679416811896</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.707203957523239</v>
+        <v>-1.7980238281186</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.946514136827052</v>
+        <v>1.892022214469836</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.277794924489235</v>
+        <v>-6.434468675869558</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4583825948478504</v>
+        <v>0.3957130942957221</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.482170957854416</v>
+        <v>-1.572990828449777</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.080554414244643</v>
+        <v>2.026062491887426</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.063160546852829</v>
+        <v>-6.219834298233151</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5489311469567304</v>
+        <v>0.4862616464046021</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.26753658021801</v>
+        <v>-1.35835645081337</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.214029841880804</v>
+        <v>2.159537919523587</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.796560189878477</v>
+        <v>-5.953233941258799</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.636765548530267</v>
+        <v>0.5740960479781387</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.26753658021801</v>
+        <v>-1.35835645081337</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.1952241006646</v>
+        <v>2.140732178307383</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.556129693073617</v>
+        <v>-5.712803444453939</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7346808238770883</v>
+        <v>0.6720113233249601</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.027106083413149</v>
+        <v>-1.11792595400851</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.341225475372393</v>
+        <v>2.286733553015177</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.313338885424171</v>
+        <v>-5.470012636804493</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8357264607716868</v>
+        <v>0.7730569602195585</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.027106083413149</v>
+        <v>-1.11792595400851</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.345154789207213</v>
+        <v>2.290662866849997</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.073733793817082</v>
+        <v>-5.230407545197404</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9322470813318624</v>
+        <v>0.8695775807797341</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9600581357446548</v>
+        <v>-1.050878006340016</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.38606214172565</v>
+        <v>2.331570219368434</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.831078205393919</v>
+        <v>-4.987751956774241</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.026307387921122</v>
+        <v>0.963637887368993</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9600581357446548</v>
+        <v>-1.050878006340016</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.383060212945644</v>
+        <v>2.328568290588427</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.611057407356908</v>
+        <v>-4.76773115873723</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.11589474414654</v>
+        <v>1.053225243594411</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8188382906766746</v>
+        <v>-0.9096581612720354</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.469371156997046</v>
+        <v>2.414879234639829</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.411808777452099</v>
+        <v>-4.568482528832421</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.211488378910287</v>
+        <v>1.148818878358158</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8188382906766746</v>
+        <v>-0.9096581612720354</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.485265339798869</v>
+        <v>2.430773417441653</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.252293673932729</v>
+        <v>-4.408967425313051</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.276440264758337</v>
+        <v>1.213770764206208</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6593231871573046</v>
+        <v>-0.7501430577526654</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.582120246350793</v>
+        <v>2.527628323993576</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.107621528832992</v>
+        <v>-4.264295280213314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.344397225359671</v>
+        <v>1.281727724807543</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5146510420575672</v>
+        <v>-0.6054709126529281</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.679011635972075</v>
+        <v>2.624519713614859</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.089852069902036</v>
+        <v>-4.246525821282358</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.266844701018775</v>
+        <v>1.204175200466647</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4968815831266116</v>
+        <v>-0.5877014537219725</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.60501300341737</v>
+        <v>2.550521081060154</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.003052572123027</v>
+        <v>-4.159726323503349</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.323964993452945</v>
+        <v>1.261295492900817</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4968815831266116</v>
+        <v>-0.5877014537219725</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.627413496739937</v>
+        <v>2.57292157438272</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.903359957394015</v>
+        <v>-4.060033708774337</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.363914440717962</v>
+        <v>1.301244940165833</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3971889683975999</v>
+        <v>-0.4880088389929607</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.687301466950756</v>
+        <v>2.632809544593539</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.971730143718025</v>
+        <v>-4.128403895098347</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.34757328866306</v>
+        <v>1.284903788110932</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3879132693613849</v>
+        <v>-0.4787331399567458</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.703873808847187</v>
+        <v>2.64938188648997</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,45 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.834187725245797</v>
+        <v>3.71417556397837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.850313714091548</v>
+        <v>-4.127618830216249</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.386576569145542</v>
+        <v>1.275654522695662</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3879132693613849</v>
+        <v>-0.4787331399567458</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.694310517479078</v>
+        <v>2.639818595121861</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="2" t="n">
+        <v>45400</v>
+      </c>
+      <c r="B1938" t="n">
+        <v>3.388879002499283</v>
+      </c>
+      <c r="C1938" t="n">
+        <v>2.753567136842101</v>
+      </c>
+      <c r="D1938" t="n">
+        <v>-4.127618830216249</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>1.275654522695662</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>-0.4787331399567458</v>
+      </c>
+      <c r="G1938" t="n">
+        <v>2.746630933828468</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-36.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.8%</t>
+          <t>138.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.3%</t>
+          <t>780.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.3%</t>
+          <t>-558.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.6%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-248.7%</t>
+          <t>-242.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.9%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.9%</t>
+          <t>-274.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-171.4%</t>
+          <t>-171.3%</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.9394593044078</v>
+        <v>-11.78278555302748</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.596516593565497</v>
+        <v>-1.533847093013367</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.589611495412947</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9713647329063866</v>
+        <v>1.025856655263603</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.65555057347905</v>
+        <v>-11.49887682209873</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.477219396955361</v>
+        <v>-1.414549896403232</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.589611495412947</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9770984371450231</v>
+        <v>1.03159035950224</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4085633232861</v>
+        <v>-11.25188957190578</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.388161759272045</v>
+        <v>-1.325492258719916</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.342624245219995</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.115553524866929</v>
+        <v>1.170045447224146</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14472645608203</v>
+        <v>-10.98805270470171</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292510493703325</v>
+        <v>-1.229840993151196</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.342624245219995</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.105670043554022</v>
+        <v>1.160161965911238</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87748465521363</v>
+        <v>-10.72081090383331</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.187448333855339</v>
+        <v>-1.12477883330321</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.342624245219995</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.103835483054648</v>
+        <v>1.158327405411864</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781944</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60167549181315</v>
+        <v>-10.44500174043283</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.077424983468606</v>
+        <v>-1.014755482916477</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.344424807536623</v>
+        <v>-3.253604936941262</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156946753048427</v>
+        <v>1.211438675405644</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57772195083719</v>
+        <v>-10.42104819945687</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.067175060932729</v>
+        <v>-1.0045055603806</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.320471266560665</v>
+        <v>-3.229651395965304</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171987383779495</v>
+        <v>1.226479306136712</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487769</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31366201251439</v>
+        <v>-10.15698826113407</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9748114017653631</v>
+        <v>-0.9121419012132339</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.965591457642508</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.317163030611421</v>
+        <v>1.371654952968637</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.606582389009557</v>
+        <v>-9.449908637629234</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6947665860237291</v>
+        <v>-0.6320970854715999</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.965591457642508</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.31437599695112</v>
+        <v>1.368867919308336</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.566398090643366</v>
+        <v>-9.409724339263043</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6783492427894116</v>
+        <v>-0.6156797422372824</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.016227029871678</v>
+        <v>-2.925407159276317</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338830199858676</v>
+        <v>1.393322122215892</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.486328295105562</v>
+        <v>-9.329654543725239</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6469545033535327</v>
+        <v>-0.5842850028014035</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.936157234333874</v>
+        <v>-2.845337363738513</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.386238898402115</v>
+        <v>1.440730820759332</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.252847072875962</v>
+        <v>-9.096173321495641</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5456375856238407</v>
+        <v>-0.482968085071712</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.702676012104276</v>
+        <v>-2.611856141508915</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.534252060577727</v>
+        <v>1.588743982934943</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.073138542732089</v>
+        <v>-8.916464791351768</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4766463838792503</v>
+        <v>-0.413976883327122</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64550450794158</v>
+        <v>-2.554684637346219</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.565662752762385</v>
+        <v>1.620154675119601</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.940863069101201</v>
+        <v>-8.78418931772088</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4283687076798683</v>
+        <v>-0.3656992071277401</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.513229034310693</v>
+        <v>-2.422409163715332</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.640395523687944</v>
+        <v>1.69488744604516</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.750263394428048</v>
+        <v>-8.593589643047727</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3493137771229704</v>
+        <v>-0.2866442765708417</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.23180948904218</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.757570389179472</v>
+        <v>1.812062311536689</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.501263595744467</v>
+        <v>-8.344589844364146</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2368075164258792</v>
+        <v>-0.1741380158737509</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.23180948904218</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.770476730403131</v>
+        <v>1.824968652760347</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.606853585517571</v>
+        <v>-8.45017983413725</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4070194419343398</v>
+        <v>-0.3443499413822111</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.337399478815284</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.579146806940049</v>
+        <v>1.633638729297266</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.625588487636168</v>
+        <v>-8.468914736255847</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3659690609046922</v>
+        <v>-0.3032995603525634</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.337399478815284</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.627691148817136</v>
+        <v>1.682183071174352</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.477648446228569</v>
+        <v>-8.320974694848248</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.42667196702982</v>
+        <v>-0.3640024664776913</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.407898433502087</v>
+        <v>-2.317078562906727</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.520004775674103</v>
+        <v>1.57449669803132</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.350756039793499</v>
+        <v>-8.194082288413178</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3846289907092699</v>
+        <v>-0.3219594901571416</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.587426233281667</v>
+        <v>1.641918155638883</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.307207633022808</v>
+        <v>-8.150533881642486</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3741702400960865</v>
+        <v>-0.3115007395439582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.580465621186574</v>
+        <v>1.63495754354379</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.065059239568949</v>
+        <v>-7.908385488188628</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2628485283334001</v>
+        <v>-0.2001790277812718</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.594927975567717</v>
+        <v>1.649419897924933</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.001829867800602</v>
+        <v>-7.84515611642028</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2430246591668661</v>
+        <v>-0.1803551586147374</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.190186156471657</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.589460096026912</v>
+        <v>1.643952018384128</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.815342175423596</v>
+        <v>-7.658668424043274</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1709314882054866</v>
+        <v>-0.1082619876533584</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.094518334690011</v>
+        <v>-2.003698464094651</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.698850805463692</v>
+        <v>1.753342727820909</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.794192976520153</v>
+        <v>-7.637519225139831</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1547708304067843</v>
+        <v>-0.09210132985465558</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.073369135786568</v>
+        <v>-1.982549265191207</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.719241303043084</v>
+        <v>1.7737332254003</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.550427534536708</v>
+        <v>-7.393753783156386</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.06148394526635581</v>
+        <v>0.00118555528577291</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.073369135786568</v>
+        <v>-1.982549265191207</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.715022011390134</v>
+        <v>1.769513933747351</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.286399467343448</v>
+        <v>-7.129725715963126</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04625159553096436</v>
+        <v>0.1089210960830931</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.780683866375254</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.838265564599722</v>
+        <v>1.892757486956939</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.036549073394373</v>
+        <v>-6.879875322014051</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1389338280942964</v>
+        <v>0.2016033286464247</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.780683866375254</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.831007639583424</v>
+        <v>1.885499561940641</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.732981584390394</v>
+        <v>-6.576307833010072</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2639599472165366</v>
+        <v>0.3266294477686653</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.780683866375254</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.834606763104073</v>
+        <v>1.88909868546129</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.65950167553838</v>
+        <v>-6.502827924158058</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.306679416811896</v>
+        <v>0.3693489173640243</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.7980238281186</v>
+        <v>-1.707203957523239</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.892022214469836</v>
+        <v>1.946514136827052</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.434468675869558</v>
+        <v>-6.391569242541225</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3957130942957221</v>
+        <v>0.4128728676270548</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.572990828449777</v>
+        <v>-1.595945275906406</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.026062491887426</v>
+        <v>2.012289823413449</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.219834298233151</v>
+        <v>-6.176934864904818</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4862616464046021</v>
+        <v>0.5034214197359348</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.35835645081337</v>
+        <v>-1.38131089827</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.159537919523587</v>
+        <v>2.14576525104961</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.953233941258799</v>
+        <v>-5.910334507930466</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5740960479781387</v>
+        <v>0.5912558213094714</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.35835645081337</v>
+        <v>-1.38131089827</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.140732178307383</v>
+        <v>2.126959509833406</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.712803444453939</v>
+        <v>-5.669904011125606</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6720113233249601</v>
+        <v>0.6891710966562927</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.11792595400851</v>
+        <v>-1.140880401465139</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.286733553015177</v>
+        <v>2.272960884541199</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.470012636804493</v>
+        <v>-5.427113203476161</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7730569602195585</v>
+        <v>0.7902167335508912</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.11792595400851</v>
+        <v>-1.140880401465139</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.290662866849997</v>
+        <v>2.276890198376019</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.230407545197404</v>
+        <v>-5.187508111869072</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8695775807797341</v>
+        <v>0.8867373541110668</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.050878006340016</v>
+        <v>-1.073832453796645</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.331570219368434</v>
+        <v>2.317797550894456</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.987751956774241</v>
+        <v>-4.944852523445908</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.963637887368993</v>
+        <v>0.9807976607003257</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.050878006340016</v>
+        <v>-1.073832453796645</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.328568290588427</v>
+        <v>2.31479562211445</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.76773115873723</v>
+        <v>-4.724831725408897</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.053225243594411</v>
+        <v>1.070385016925744</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9096581612720354</v>
+        <v>-0.9326126087286646</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.414879234639829</v>
+        <v>2.401106566165852</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.568482528832421</v>
+        <v>-4.525583095504088</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.148818878358158</v>
+        <v>1.165978651689491</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9096581612720354</v>
+        <v>-0.9326126087286646</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.430773417441653</v>
+        <v>2.417000748967675</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.408967425313051</v>
+        <v>-4.366067991984719</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.213770764206208</v>
+        <v>1.230930537537541</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7501430577526654</v>
+        <v>-0.7730975052092947</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.527628323993576</v>
+        <v>2.513855655519599</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.264295280213314</v>
+        <v>-4.221395846884981</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.281727724807543</v>
+        <v>1.298887498138876</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6054709126529281</v>
+        <v>-0.6284253601095573</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.624519713614859</v>
+        <v>2.610747045140881</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.246525821282358</v>
+        <v>-4.203626387954025</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.204175200466647</v>
+        <v>1.22133497379798</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5877014537219725</v>
+        <v>-0.6106559011786017</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.550521081060154</v>
+        <v>2.536748412586176</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.159726323503349</v>
+        <v>-4.116826890175016</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.261295492900817</v>
+        <v>1.278455266232149</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5877014537219725</v>
+        <v>-0.6106559011786017</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.57292157438272</v>
+        <v>2.559148905908742</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.060033708774337</v>
+        <v>-4.017134275446004</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.301244940165833</v>
+        <v>1.318404713497166</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4880088389929607</v>
+        <v>-0.5109632864495899</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.632809544593539</v>
+        <v>2.619036876119562</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.128403895098347</v>
+        <v>-4.085504461770014</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.284903788110932</v>
+        <v>1.302063561442264</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.5016875874133749</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.64938188648997</v>
+        <v>2.635609218015992</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417556397837</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.127618830216249</v>
+        <v>-3.964088032143538</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.275654522695662</v>
+        <v>1.341066841924746</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.5016875874133749</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.639818595121861</v>
+        <v>2.626045926647884</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.388879002499283</v>
+        <v>3.393672189050418</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.753567136842101</v>
+        <v>2.753966230878463</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.127618830216249</v>
+        <v>-3.964088032143538</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.275654522695662</v>
+        <v>1.341066841924746</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.5016875874133749</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.746630933828468</v>
+        <v>2.747030027864831</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>137.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.7%</t>
+          <t>788.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-558.0%</t>
+          <t>-547.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-242.1%</t>
+          <t>-238.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-332.5%</t>
+          <t>-317.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-156.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-274.2%</t>
+          <t>-257.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-191.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-140.3%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.106599156023547</v>
+        <v>-3.959921622742516</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.492969633139954</v>
+        <v>1.551640646452366</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8659163920100523</v>
+        <v>-0.7192388587290219</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.616415884657089</v>
+        <v>2.704422404625707</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.415833259019598</v>
+        <v>-4.269155725738567</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.371048918641793</v>
+        <v>1.429719931954205</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8659163920100523</v>
+        <v>-0.7192388587290219</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.618188811357348</v>
+        <v>2.706195331325966</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.847639052169385</v>
+        <v>-4.700961518888355</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.184659488849283</v>
+        <v>1.243330502161695</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.002333888451319</v>
+        <v>-0.8556563551702889</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.522671200959993</v>
+        <v>2.610677720928611</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.174071581037129</v>
+        <v>-5.027394047756099</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.042371252304275</v>
+        <v>1.101042265616688</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.084802138958467</v>
+        <v>-0.9381246056774371</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.461475025657794</v>
+        <v>2.549481545626413</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.509734228267582</v>
+        <v>-5.363056694986551</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9066867850680596</v>
+        <v>0.965357798380472</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.084802138958467</v>
+        <v>-0.9381246056774371</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.460055617313759</v>
+        <v>2.548062137282378</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.873360473167895</v>
+        <v>-5.726682939886865</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7677238473421761</v>
+        <v>0.8263948606545881</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.183023775825593</v>
+        <v>-1.036346242544563</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.407610195427726</v>
+        <v>2.495616715396344</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.238487855806642</v>
+        <v>-6.091810322525611</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6209274092925088</v>
+        <v>0.6795984226049208</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.479334560124606</v>
+        <v>-1.332657026843575</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.229078239854149</v>
+        <v>2.317084759822768</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.64707663298732</v>
+        <v>-6.500399099706289</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4562534424349964</v>
+        <v>0.5149244557474084</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.741245804024254</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.982686517560501</v>
+        <v>2.07069303752912</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.060059117128413</v>
+        <v>-6.913381583847383</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2862458812500197</v>
+        <v>0.3449168945624317</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.741245804024254</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.977871950031962</v>
+        <v>2.06587847000058</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.476450991415411</v>
+        <v>-7.329773458134381</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.117683182144098</v>
+        <v>0.17635419545651</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.741245804024254</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.975866000640839</v>
+        <v>2.063872520609458</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.853128001945255</v>
+        <v>-7.706450468664225</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02272893139916077</v>
+        <v>0.03594208191325121</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.741245804024254</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.986124691309518</v>
+        <v>2.074131211278137</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.199002823930064</v>
+        <v>-8.052325290649033</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.164979295047389</v>
+        <v>-0.106308281734977</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.741245804024254</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.982224256455214</v>
+        <v>2.070230776423832</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.511827623175042</v>
+        <v>-8.365150089894012</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2917042946903794</v>
+        <v>-0.2330332813779674</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.741245804024254</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.980629176510215</v>
+        <v>2.068635696478833</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.808488964985241</v>
+        <v>-8.66181143170421</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4065898554852505</v>
+        <v>-0.3479188421728385</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.809988939758132</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.943162270999096</v>
+        <v>2.031168790967714</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.241838073095476</v>
+        <v>-9.095160539814445</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.583955803263748</v>
+        <v>-0.5252847899513355</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.809988939758132</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.939135966464693</v>
+        <v>2.027142486433311</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.624839461838107</v>
+        <v>-9.478161928557077</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7372584600823844</v>
+        <v>-0.6785874467699724</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.809988939758132</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.939033865143108</v>
+        <v>2.027040385111727</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.999824788009384</v>
+        <v>-9.853147254728354</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8846810745794653</v>
+        <v>-0.8260100612670529</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.18497426592941</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.716614185411772</v>
+        <v>1.80462070538039</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.35935511051339</v>
+        <v>-10.21267757723236</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.023142900283015</v>
+        <v>-0.9644718869706033</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.18497426592941</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.721964488709822</v>
+        <v>1.80997100867844</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.6857551391784</v>
+        <v>-10.53907760589737</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.145786891791844</v>
+        <v>-1.087115878479431</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.658051827875453</v>
+        <v>-2.511374294594423</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.534040491467992</v>
+        <v>1.62204701143661</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.9049041072526</v>
+        <v>-10.75822657397157</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.230404728399753</v>
+        <v>-1.171733715087341</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.73052326266862</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.405592861245242</v>
+        <v>1.49359938121386</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.90121318229619</v>
+        <v>-10.75453564901516</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.22892835841719</v>
+        <v>-1.170257345104777</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.73052326266862</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.405592861245242</v>
+        <v>1.49359938121386</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.10547135762605</v>
+        <v>-10.95879382434502</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.305118431430492</v>
+        <v>-1.24644741811808</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.00483974056364</v>
+        <v>-2.858162207282609</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.334522691595491</v>
+        <v>1.422529211564109</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.32350912925723</v>
+        <v>-11.1768315959762</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.387850985598527</v>
+        <v>-1.329179972286115</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.179610508659539</v>
+        <v>-3.032932975378508</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.234142785222388</v>
+        <v>1.322149305191006</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.25003929758978</v>
+        <v>-11.10336176430875</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.343091351438127</v>
+        <v>-1.284420338125714</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.10614067699209</v>
+        <v>-2.95946314371106</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.293596385716278</v>
+        <v>1.381602905684896</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.42516371497632</v>
+        <v>-11.27848618169529</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.398585897645227</v>
+        <v>-1.339914884332815</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.281265094378634</v>
+        <v>-3.134587561097604</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.203076956031869</v>
+        <v>1.291083476000487</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.65961580899081</v>
+        <v>-11.51293827570978</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.499585900152619</v>
+        <v>-1.440914886840206</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.281265094378634</v>
+        <v>-3.134587561097604</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.195857791130273</v>
+        <v>1.283864311098891</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.94741965352805</v>
+        <v>-11.80074212024702</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.621379628741491</v>
+        <v>-1.562708615429079</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.569068938915872</v>
+        <v>-3.422391405634842</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.016503293633954</v>
+        <v>1.104509813602572</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.17724410069187</v>
+        <v>-12.03056656741084</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.712193617768464</v>
+        <v>-1.653522604456052</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.731716475986033</v>
+        <v>-3.585038942705002</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9200305612304134</v>
+        <v>1.008037081199032</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.40927302042814</v>
+        <v>-12.26259548714711</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.802311457033854</v>
+        <v>-1.743640443721442</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.647051639893426</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8855166715464744</v>
+        <v>0.9735231915150924</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.35725750645932</v>
+        <v>-12.21057997317829</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.777514915759928</v>
+        <v>-1.718843902447516</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.647051639893426</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8895070072328752</v>
+        <v>0.9775135272014932</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.49892934818344</v>
+        <v>-12.35225181490241</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.835658879348318</v>
+        <v>-1.776987866035906</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.647051639893426</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8880317803341335</v>
+        <v>0.9760383003027515</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.59783608864272</v>
+        <v>-12.45115855536169</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.860168165367156</v>
+        <v>-1.801497152054744</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.892635913633731</v>
+        <v>-3.745958380352701</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8437411462234405</v>
+        <v>0.931747666192059</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.39868398140562</v>
+        <v>-12.25200644812459</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.793558456119</v>
+        <v>-1.734887442806587</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.727313387683918</v>
+        <v>-3.580635854402888</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9298835281466458</v>
+        <v>1.017890048115264</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.17283882868621</v>
+        <v>-12.02616129540518</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.693641321995027</v>
+        <v>-1.634970308682614</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.538709178815724</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9646186065351525</v>
+        <v>1.05262512650377</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.88656401636351</v>
+        <v>-11.73988648308248</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.57799225250989</v>
+        <v>-1.519321239197477</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.538709178815724</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9657577510912114</v>
+        <v>1.053764271059829</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78278555302748</v>
+        <v>-11.79278177112677</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.533847093013367</v>
+        <v>-1.537845580253084</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.589611495412947</v>
+        <v>-3.533753832727278</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.025856655263603</v>
+        <v>1.059371252875005</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.49887682209873</v>
+        <v>-11.50887304019802</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.414549896403232</v>
+        <v>-1.418548383642948</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.589611495412947</v>
+        <v>-3.533753832727278</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.03159035950224</v>
+        <v>1.065104957113642</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.25188957190578</v>
+        <v>-11.26188579000507</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.325492258719916</v>
+        <v>-1.329490745959633</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.342624245219995</v>
+        <v>-3.286766582534326</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.170045447224146</v>
+        <v>1.203560044835547</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.98805270470171</v>
+        <v>-10.998048922801</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.229840993151196</v>
+        <v>-1.233839480390912</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.342624245219995</v>
+        <v>-3.286766582534326</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.160161965911238</v>
+        <v>1.19367656352264</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.72081090383331</v>
+        <v>-10.7308071219326</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.12477883330321</v>
+        <v>-1.128777320542926</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.342624245219995</v>
+        <v>-3.286766582534326</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.158327405411864</v>
+        <v>1.191842003023266</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.44500174043283</v>
+        <v>-10.45499795853212</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.014755482916477</v>
+        <v>-1.018753970156193</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.253604936941262</v>
+        <v>-3.197747274255592</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.211438675405644</v>
+        <v>1.244953273017045</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.42104819945687</v>
+        <v>-10.43104441755616</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.0045055603806</v>
+        <v>-1.008504047620316</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.229651395965304</v>
+        <v>-3.173793733279635</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.226479306136712</v>
+        <v>1.259993903748114</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.15698826113407</v>
+        <v>-10.16698447923336</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9121419012132339</v>
+        <v>-0.9161403884529502</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.965591457642508</v>
+        <v>-2.909733794956839</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.371654952968637</v>
+        <v>1.405169550580039</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.449908637629234</v>
+        <v>-9.459904855728524</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6320970854715999</v>
+        <v>-0.6360955727113162</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.965591457642508</v>
+        <v>-2.909733794956839</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.368867919308336</v>
+        <v>1.402382516919738</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.409724339263043</v>
+        <v>-9.419720557362334</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6156797422372824</v>
+        <v>-0.6196782294769987</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.925407159276317</v>
+        <v>-2.869549496590648</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.393322122215892</v>
+        <v>1.426836719827294</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.329654543725239</v>
+        <v>-9.339650761824529</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5842850028014035</v>
+        <v>-0.5882834900411198</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.845337363738513</v>
+        <v>-2.789479701052844</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.440730820759332</v>
+        <v>1.474245418370733</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.096173321495641</v>
+        <v>-9.10616953959493</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.482968085071712</v>
+        <v>-0.4869665723114278</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.611856141508915</v>
+        <v>-2.555998478823245</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.588743982934943</v>
+        <v>1.622258580546345</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.916464791351768</v>
+        <v>-8.926461009451057</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.413976883327122</v>
+        <v>-0.4179753705668374</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.554684637346219</v>
+        <v>-2.498826974660549</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.620154675119601</v>
+        <v>1.653669272731003</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.78418931772088</v>
+        <v>-8.794185535820169</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3656992071277401</v>
+        <v>-0.3696976943674555</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.422409163715332</v>
+        <v>-2.366551501029663</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.69488744604516</v>
+        <v>1.728402043656562</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.593589643047727</v>
+        <v>-8.603585861147016</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2866442765708417</v>
+        <v>-0.2906427638105575</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.23180948904218</v>
+        <v>-2.17595182635651</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.812062311536689</v>
+        <v>1.84557690914809</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.344589844364146</v>
+        <v>-8.354586062463435</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1741380158737509</v>
+        <v>-0.1781365031134663</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.23180948904218</v>
+        <v>-2.17595182635651</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.824968652760347</v>
+        <v>1.858483250371749</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.45017983413725</v>
+        <v>-8.460176052236539</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3443499413822111</v>
+        <v>-0.3483484286219269</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.337399478815284</v>
+        <v>-2.281541816129615</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.633638729297266</v>
+        <v>1.667153326908668</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.468914736255847</v>
+        <v>-8.478910954355136</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3032995603525634</v>
+        <v>-0.3072980475922793</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.337399478815284</v>
+        <v>-2.281541816129615</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.682183071174352</v>
+        <v>1.715697668785754</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.320974694848248</v>
+        <v>-8.330970912947537</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3640024664776913</v>
+        <v>-0.3680009537174072</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.317078562906727</v>
+        <v>-2.261220900221057</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.57449669803132</v>
+        <v>1.608011295642721</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.194082288413178</v>
+        <v>-8.204078506512467</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3219594901571416</v>
+        <v>-0.3259579773968571</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.134328493785987</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.641918155638883</v>
+        <v>1.675432753250285</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.150533881642486</v>
+        <v>-8.160530099741775</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3115007395439582</v>
+        <v>-0.3154992267836736</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.134328493785987</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.63495754354379</v>
+        <v>1.668472141155192</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.908385488188628</v>
+        <v>-7.918381706287917</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2001790277812718</v>
+        <v>-0.2041775150209872</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.134328493785987</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.649419897924933</v>
+        <v>1.682934495536335</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.84515611642028</v>
+        <v>-7.855152334519569</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1803551586147374</v>
+        <v>-0.1843536458544532</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.190186156471657</v>
+        <v>-2.134328493785987</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.643952018384128</v>
+        <v>1.67746661599553</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.658668424043274</v>
+        <v>-7.668664642142563</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1082619876533584</v>
+        <v>-0.1122604748930738</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.003698464094651</v>
+        <v>-1.947840801408981</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.753342727820909</v>
+        <v>1.78685732543231</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.637519225139831</v>
+        <v>-7.647515443239119</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.09210132985465558</v>
+        <v>-0.09609981709437143</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.982549265191207</v>
+        <v>-1.926691602505538</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.7737332254003</v>
+        <v>1.807247823011702</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.393753783156386</v>
+        <v>-7.403750001255675</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.00118555528577291</v>
+        <v>-0.002812931953942943</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.982549265191207</v>
+        <v>-1.926691602505538</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.769513933747351</v>
+        <v>1.803028531358752</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.129725715963126</v>
+        <v>-7.139721934062415</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1089210960830931</v>
+        <v>0.1049226088433772</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.780683866375254</v>
+        <v>-1.724826203689584</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.892757486956939</v>
+        <v>1.926272084568341</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.879875322014051</v>
+        <v>-6.88987154011334</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2016033286464247</v>
+        <v>0.1976048414067093</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.780683866375254</v>
+        <v>-1.724826203689584</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.885499561940641</v>
+        <v>1.919014159552042</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.576307833010072</v>
+        <v>-6.586304051109361</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3266294477686653</v>
+        <v>0.3226309605289495</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.780683866375254</v>
+        <v>-1.724826203689584</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.88909868546129</v>
+        <v>1.922613283072692</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.502827924158058</v>
+        <v>-6.512824142257347</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3693489173640243</v>
+        <v>0.3653504301243089</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.707203957523239</v>
+        <v>-1.65134629483757</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.946514136827052</v>
+        <v>1.980028734438454</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.391569242541225</v>
+        <v>-6.287791142588524</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4128728676270548</v>
+        <v>0.454384107608135</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.595945275906406</v>
+        <v>-1.426313295168747</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.012289823413449</v>
+        <v>2.114069011856044</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.176934864904818</v>
+        <v>-6.073156764952118</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5034214197359348</v>
+        <v>0.544932659717015</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.38131089827</v>
+        <v>-1.21167891753234</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.14576525104961</v>
+        <v>2.247544439492206</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.910334507930466</v>
+        <v>-5.806556407977766</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5912558213094714</v>
+        <v>0.6327670612905516</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.38131089827</v>
+        <v>-1.21167891753234</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.126959509833406</v>
+        <v>2.228738698276001</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.669904011125606</v>
+        <v>-5.566125911172906</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6891710966562927</v>
+        <v>0.7306823366373729</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.140880401465139</v>
+        <v>-0.9712484207274796</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.272960884541199</v>
+        <v>2.374740072983795</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.427113203476161</v>
+        <v>-5.32333510352346</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7902167335508912</v>
+        <v>0.8317279735319714</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.140880401465139</v>
+        <v>-0.9712484207274796</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.276890198376019</v>
+        <v>2.378669386818615</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.187508111869072</v>
+        <v>-5.083730011916371</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8867373541110668</v>
+        <v>0.928248594092147</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.073832453796645</v>
+        <v>-0.9042004730589851</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.317797550894456</v>
+        <v>2.419576739337052</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.944852523445908</v>
+        <v>-4.841074423493207</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9807976607003257</v>
+        <v>1.022308900681406</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.073832453796645</v>
+        <v>-0.9042004730589851</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.31479562211445</v>
+        <v>2.416574810557045</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.724831725408897</v>
+        <v>-4.621053625456197</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.070385016925744</v>
+        <v>1.111896256906824</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9326126087286646</v>
+        <v>-0.7629806279910049</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.401106566165852</v>
+        <v>2.502885754608448</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.525583095504088</v>
+        <v>-4.421804995551388</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.165978651689491</v>
+        <v>1.207489891670571</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9326126087286646</v>
+        <v>-0.7629806279910049</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.417000748967675</v>
+        <v>2.518779937410271</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.366067991984719</v>
+        <v>-4.262289892032018</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.230930537537541</v>
+        <v>1.272441777518621</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7730975052092947</v>
+        <v>-0.6034655244716349</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.513855655519599</v>
+        <v>2.615634843962195</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.221395846884981</v>
+        <v>-4.117617746932281</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.298887498138876</v>
+        <v>1.340398738119956</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6284253601095573</v>
+        <v>-0.4587933793718975</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.610747045140881</v>
+        <v>2.712526233583477</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.203626387954025</v>
+        <v>-4.099848288001325</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22133497379798</v>
+        <v>1.26284621377906</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6106559011786017</v>
+        <v>-0.441023920440942</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.536748412586176</v>
+        <v>2.638527601028772</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.116826890175016</v>
+        <v>-4.013048790222316</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.278455266232149</v>
+        <v>1.31996650621323</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6106559011786017</v>
+        <v>-0.441023920440942</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.559148905908742</v>
+        <v>2.660928094351338</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.017134275446004</v>
+        <v>-3.913356175493304</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.318404713497166</v>
+        <v>1.359915953478246</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5109632864495899</v>
+        <v>-0.3413313057119302</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.619036876119562</v>
+        <v>2.720816064562158</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.085504461770014</v>
+        <v>-3.981726361817314</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.302063561442264</v>
+        <v>1.343574801423344</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5016875874133749</v>
+        <v>-0.3320556066757153</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.635609218015992</v>
+        <v>2.737388406458588</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.964088032143538</v>
+        <v>-3.860309932190837</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.341066841924746</v>
+        <v>1.382578081905826</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5016875874133749</v>
+        <v>-0.3320556066757153</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.626045926647884</v>
+        <v>2.72782511509048</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.393672189050418</v>
+        <v>3.7323400503571</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.753966230878463</v>
+        <v>3.063699736886408</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.964088032143538</v>
+        <v>-3.860309932190837</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.341066841924746</v>
+        <v>1.382578081905826</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5016875874133749</v>
+        <v>-0.3320556066757153</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.747030027864831</v>
+        <v>3.056763533872776</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776675</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.7%</t>
+          <t>138.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>788.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-547.6%</t>
+          <t>-559.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-238.0%</t>
+          <t>-241.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-317.8%</t>
+          <t>-332.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.6%</t>
+          <t>-161.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.2%</t>
+          <t>-271.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.1%</t>
+          <t>-199.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-140.3%</t>
+          <t>-181.3%</t>
         </is>
       </c>
     </row>
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.959921622742516</v>
+        <v>-4.106599156023547</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.551640646452366</v>
+        <v>1.492969633139954</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7192388587290219</v>
+        <v>-0.8659163920100523</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.704422404625707</v>
+        <v>2.616415884657089</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.269155725738567</v>
+        <v>-4.283500627543588</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.429719931954205</v>
+        <v>1.423981971232197</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7192388587290219</v>
+        <v>-0.8659163920100523</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.706195331325966</v>
+        <v>2.618188811357348</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.700961518888355</v>
+        <v>-4.715306420693375</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.243330502161695</v>
+        <v>1.237592541439686</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8556563551702889</v>
+        <v>-1.002333888451319</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.610677720928611</v>
+        <v>2.522671200959993</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.027394047756099</v>
+        <v>-5.041738949561119</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.101042265616688</v>
+        <v>1.09530430489468</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9381246056774371</v>
+        <v>-1.084802138958467</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.549481545626413</v>
+        <v>2.461475025657794</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.363056694986551</v>
+        <v>-5.377401596791572</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.965357798380472</v>
+        <v>0.9596198376584639</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9381246056774371</v>
+        <v>-1.084802138958467</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.548062137282378</v>
+        <v>2.460055617313759</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.726682939886865</v>
+        <v>-5.741027841691885</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8263948606545881</v>
+        <v>0.8206568999325801</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.036346242544563</v>
+        <v>-1.183023775825593</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495616715396344</v>
+        <v>2.407610195427726</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.091810322525611</v>
+        <v>-6.106155224330632</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6795984226049208</v>
+        <v>0.6738604618829127</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332657026843575</v>
+        <v>-1.479334560124606</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317084759822768</v>
+        <v>2.229078239854149</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.500399099706289</v>
+        <v>-6.514744001511311</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5149244557474084</v>
+        <v>0.5091864950253999</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741245804024254</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.07069303752912</v>
+        <v>1.982686517560501</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.913381583847383</v>
+        <v>-6.927726485652404</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3449168945624317</v>
+        <v>0.3391789338404232</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741245804024254</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.06587847000058</v>
+        <v>1.977871950031962</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.329773458134381</v>
+        <v>-7.344118359939402</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.17635419545651</v>
+        <v>0.1706162347345015</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741245804024254</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063872520609458</v>
+        <v>1.975866000640839</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.706450468664225</v>
+        <v>-7.720795370469246</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03594208191325121</v>
+        <v>0.03020412119124272</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741245804024254</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074131211278137</v>
+        <v>1.986124691309518</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.052325290649033</v>
+        <v>-8.066670192454055</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.106308281734977</v>
+        <v>-0.1120462424569855</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741245804024254</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070230776423832</v>
+        <v>1.982224256455214</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.365150089894012</v>
+        <v>-8.379494991699033</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2330332813779674</v>
+        <v>-0.2387712420999759</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741245804024254</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.068635696478833</v>
+        <v>1.980629176510215</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.66181143170421</v>
+        <v>-8.676156333509232</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3479188421728385</v>
+        <v>-0.353656802894847</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809988939758132</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031168790967714</v>
+        <v>1.943162270999096</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.095160539814445</v>
+        <v>-9.109505441619467</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5252847899513355</v>
+        <v>-0.531022750673344</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809988939758132</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027142486433311</v>
+        <v>1.939135966464693</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.478161928557077</v>
+        <v>-9.492506830362098</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6785874467699724</v>
+        <v>-0.6843254074919809</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809988939758132</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027040385111727</v>
+        <v>1.939033865143108</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.853147254728354</v>
+        <v>-9.867492156533375</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8260100612670529</v>
+        <v>-0.8317480219890614</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.18497426592941</v>
+        <v>-2.33165179921044</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.80462070538039</v>
+        <v>1.716614185411772</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.21267757723236</v>
+        <v>-10.22702247903738</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9644718869706033</v>
+        <v>-0.9702098476926118</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.18497426592941</v>
+        <v>-2.33165179921044</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.80997100867844</v>
+        <v>1.721964488709822</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53907760589737</v>
+        <v>-10.55342250770239</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.087115878479431</v>
+        <v>-1.092853839201439</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.511374294594423</v>
+        <v>-2.658051827875453</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.62204701143661</v>
+        <v>1.534040491467992</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.75822657397157</v>
+        <v>-10.77257147577659</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.171733715087341</v>
+        <v>-1.17747167580935</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.73052326266862</v>
+        <v>-2.877200795949651</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.49359938121386</v>
+        <v>1.405592861245242</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.75453564901516</v>
+        <v>-10.76888055082018</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.170257345104777</v>
+        <v>-1.175995305826785</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.73052326266862</v>
+        <v>-2.877200795949651</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.49359938121386</v>
+        <v>1.405592861245242</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95879382434502</v>
+        <v>-10.97313872615004</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.24644741811808</v>
+        <v>-1.252185378840089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.858162207282609</v>
+        <v>-3.00483974056364</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.422529211564109</v>
+        <v>1.334522691595491</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1768315959762</v>
+        <v>-11.19117649778122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.329179972286115</v>
+        <v>-1.334917933008124</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.032932975378508</v>
+        <v>-3.179610508659539</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.322149305191006</v>
+        <v>1.234142785222388</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.10336176430875</v>
+        <v>-11.11770666611377</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.284420338125714</v>
+        <v>-1.290158298847722</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.95946314371106</v>
+        <v>-3.10614067699209</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.381602905684896</v>
+        <v>1.293596385716278</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.27848618169529</v>
+        <v>-11.29283108350031</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.339914884332815</v>
+        <v>-1.345652845054824</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.134587561097604</v>
+        <v>-3.281265094378634</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.291083476000487</v>
+        <v>1.203076956031869</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.51293827570978</v>
+        <v>-11.5272831775148</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.440914886840206</v>
+        <v>-1.446652847562215</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.134587561097604</v>
+        <v>-3.281265094378634</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.283864311098891</v>
+        <v>1.195857791130273</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.80074212024702</v>
+        <v>-11.81508702205204</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.562708615429079</v>
+        <v>-1.568446576151087</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.422391405634842</v>
+        <v>-3.569068938915872</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.104509813602572</v>
+        <v>1.016503293633954</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.03056656741084</v>
+        <v>-12.04491146921587</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.653522604456052</v>
+        <v>-1.659260565178061</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.585038942705002</v>
+        <v>-3.731716475986033</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.008037081199032</v>
+        <v>0.9200305612304134</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.26259548714711</v>
+        <v>-12.27694038895213</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.743640443721442</v>
+        <v>-1.749378404443451</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.647051639893426</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9735231915150924</v>
+        <v>0.8855166715464744</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.21057997317829</v>
+        <v>-12.22492487498331</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.718843902447516</v>
+        <v>-1.724581863169525</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.647051639893426</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9775135272014932</v>
+        <v>0.8895070072328752</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.35225181490241</v>
+        <v>-12.36659671670743</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.776987866035906</v>
+        <v>-1.782725826757915</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.647051639893426</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9760383003027515</v>
+        <v>0.8880317803341335</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.45115855536169</v>
+        <v>-12.46550345716671</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.801497152054744</v>
+        <v>-1.807235112776752</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.745958380352701</v>
+        <v>-3.892635913633731</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.931747666192059</v>
+        <v>0.8437411462234405</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.25200644812459</v>
+        <v>-12.26635134992961</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.734887442806587</v>
+        <v>-1.740625403528596</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.580635854402888</v>
+        <v>-3.727313387683918</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.017890048115264</v>
+        <v>0.9298835281466458</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.02616129540518</v>
+        <v>-12.0405061972102</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.634970308682614</v>
+        <v>-1.640708269404623</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.538709178815724</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.05262512650377</v>
+        <v>0.9646186065351525</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73988648308248</v>
+        <v>-11.7542313848875</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.519321239197477</v>
+        <v>-1.525059199919486</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.538709178815724</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.053764271059829</v>
+        <v>0.9657577510912114</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116212</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.79278177112677</v>
+        <v>-11.80712667293179</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.537845580253084</v>
+        <v>-1.543583540975092</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.533753832727278</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.059371252875005</v>
+        <v>0.9713647329063866</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081563</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50887304019802</v>
+        <v>-11.52321794200304</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.418548383642948</v>
+        <v>-1.424286344364956</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.533753832727278</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.065104957113642</v>
+        <v>0.9770984371450231</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.26188579000507</v>
+        <v>-11.27623069181009</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.329490745959633</v>
+        <v>-1.335228706681641</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.286766582534326</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.203560044835547</v>
+        <v>1.115553524866929</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702407</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.998048922801</v>
+        <v>-11.01239382460602</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.233839480390912</v>
+        <v>-1.239577441112921</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.286766582534326</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.19367656352264</v>
+        <v>1.105670043554022</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906223</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.7308071219326</v>
+        <v>-10.74515202373762</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.128777320542926</v>
+        <v>-1.134515281264935</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.286766582534326</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.191842003023266</v>
+        <v>1.103835483054648</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.45499795853212</v>
+        <v>-10.46934286033714</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.018753970156193</v>
+        <v>-1.024491930878202</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.197747274255592</v>
+        <v>-3.344424807536623</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.244953273017045</v>
+        <v>1.156946753048427</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567238</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.43104441755616</v>
+        <v>-10.44538931936118</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.008504047620316</v>
+        <v>-1.014242008342325</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.173793733279635</v>
+        <v>-3.320471266560665</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.259993903748114</v>
+        <v>1.171987383779495</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.16698447923336</v>
+        <v>-10.18132938103838</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9161403884529502</v>
+        <v>-0.9218783491749587</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.909733794956839</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.405169550580039</v>
+        <v>1.317163030611421</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.459904855728524</v>
+        <v>-9.474249757533546</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6360955727113162</v>
+        <v>-0.6418335334333247</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.909733794956839</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.402382516919738</v>
+        <v>1.31437599695112</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.419720557362334</v>
+        <v>-9.434065459167355</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6196782294769987</v>
+        <v>-0.6254161901990072</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.869549496590648</v>
+        <v>-3.016227029871678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.426836719827294</v>
+        <v>1.338830199858676</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.339650761824529</v>
+        <v>-9.353995663629551</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5882834900411198</v>
+        <v>-0.5940214507631283</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.789479701052844</v>
+        <v>-2.936157234333874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.474245418370733</v>
+        <v>1.386238898402115</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.10616953959493</v>
+        <v>-9.120514441399951</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4869665723114278</v>
+        <v>-0.4927045330334363</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.555998478823245</v>
+        <v>-2.702676012104276</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.622258580546345</v>
+        <v>1.534252060577727</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.926461009451057</v>
+        <v>-8.940805911256078</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4179753705668374</v>
+        <v>-0.4237133312888459</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.498826974660549</v>
+        <v>-2.64550450794158</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.653669272731003</v>
+        <v>1.565662752762385</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.794185535820169</v>
+        <v>-8.808530437625191</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3696976943674555</v>
+        <v>-0.375435655089464</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.366551501029663</v>
+        <v>-2.513229034310693</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.728402043656562</v>
+        <v>1.640395523687944</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.603585861147016</v>
+        <v>-8.617930762952037</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2906427638105575</v>
+        <v>-0.296380724532566</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.17595182635651</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.84557690914809</v>
+        <v>1.757570389179472</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.354586062463435</v>
+        <v>-8.368930964268456</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1781365031134663</v>
+        <v>-0.1838744638354748</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.17595182635651</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.858483250371749</v>
+        <v>1.770476730403131</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.460176052236539</v>
+        <v>-8.47452095404156</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3483484286219269</v>
+        <v>-0.3540863893439354</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.281541816129615</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.667153326908668</v>
+        <v>1.579146806940049</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.478910954355136</v>
+        <v>-8.493255856160157</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3072980475922793</v>
+        <v>-0.3130360083142878</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.281541816129615</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.715697668785754</v>
+        <v>1.627691148817136</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.330970912947537</v>
+        <v>-8.345315814752558</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3680009537174072</v>
+        <v>-0.3737389144394156</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.261220900221057</v>
+        <v>-2.407898433502087</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.608011295642721</v>
+        <v>1.520004775674103</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.204078506512467</v>
+        <v>-8.218423408317488</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3259579773968571</v>
+        <v>-0.3316959381188656</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.134328493785987</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.675432753250285</v>
+        <v>1.587426233281667</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.160530099741775</v>
+        <v>-8.174875001546797</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3154992267836736</v>
+        <v>-0.3212371875056821</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.134328493785987</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.668472141155192</v>
+        <v>1.580465621186574</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.918381706287917</v>
+        <v>-7.932726608092938</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2041775150209872</v>
+        <v>-0.2099154757429957</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.134328493785987</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.682934495536335</v>
+        <v>1.594927975567717</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.855152334519569</v>
+        <v>-7.86949723632459</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1843536458544532</v>
+        <v>-0.1900916065764617</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.134328493785987</v>
+        <v>-2.281006027067018</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.67746661599553</v>
+        <v>1.589460096026912</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.668664642142563</v>
+        <v>-7.683009543947584</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1122604748930738</v>
+        <v>-0.1179984356150823</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.947840801408981</v>
+        <v>-2.094518334690011</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.78685732543231</v>
+        <v>1.698850805463692</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.647515443239119</v>
+        <v>-7.661860345044141</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.09609981709437143</v>
+        <v>-0.1018377778163799</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.926691602505538</v>
+        <v>-2.073369135786568</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.807247823011702</v>
+        <v>1.719241303043084</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.403750001255675</v>
+        <v>-7.418094903060696</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.002812931953942943</v>
+        <v>-0.008550892675951438</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.926691602505538</v>
+        <v>-2.073369135786568</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.803028531358752</v>
+        <v>1.715022011390134</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.139721934062415</v>
+        <v>-7.154066835867436</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1049226088433772</v>
+        <v>0.09918464812136873</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.724826203689584</v>
+        <v>-1.871503736970614</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.926272084568341</v>
+        <v>1.838265564599722</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.88987154011334</v>
+        <v>-6.904216441918361</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1976048414067093</v>
+        <v>0.1918668806847008</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.724826203689584</v>
+        <v>-1.871503736970614</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.919014159552042</v>
+        <v>1.831007639583424</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.586304051109361</v>
+        <v>-6.600648952914383</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3226309605289495</v>
+        <v>0.316892999806941</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.724826203689584</v>
+        <v>-1.871503736970614</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.922613283072692</v>
+        <v>1.834606763104073</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.512824142257347</v>
+        <v>-6.527169044062369</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3653504301243089</v>
+        <v>0.3596124694023004</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.65134629483757</v>
+        <v>-1.7980238281186</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.980028734438454</v>
+        <v>1.892022214469836</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.287791142588524</v>
+        <v>-6.302136044393546</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.454384107608135</v>
+        <v>0.4486461468861265</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.426313295168747</v>
+        <v>-1.572990828449777</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.114069011856044</v>
+        <v>2.026062491887426</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.073156764952118</v>
+        <v>-6.087501666757139</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.544932659717015</v>
+        <v>0.5391946989950065</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.21167891753234</v>
+        <v>-1.35835645081337</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.247544439492206</v>
+        <v>2.159537919523587</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.806556407977766</v>
+        <v>-5.820901309782787</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6327670612905516</v>
+        <v>0.6270291005685431</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.21167891753234</v>
+        <v>-1.35835645081337</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.228738698276001</v>
+        <v>2.140732178307383</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.566125911172906</v>
+        <v>-5.580470812977927</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7306823366373729</v>
+        <v>0.7249443759153644</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9712484207274796</v>
+        <v>-1.11792595400851</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.374740072983795</v>
+        <v>2.286733553015177</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.32333510352346</v>
+        <v>-5.337680005328481</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8317279735319714</v>
+        <v>0.8259900128099629</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9712484207274796</v>
+        <v>-1.11792595400851</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.378669386818615</v>
+        <v>2.290662866849997</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.083730011916371</v>
+        <v>-5.098074913721392</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.928248594092147</v>
+        <v>0.9225106333701385</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9042004730589851</v>
+        <v>-1.050878006340016</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.419576739337052</v>
+        <v>2.331570219368434</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.841074423493207</v>
+        <v>-4.855419325298229</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.022308900681406</v>
+        <v>1.016570939959397</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9042004730589851</v>
+        <v>-1.050878006340016</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.416574810557045</v>
+        <v>2.328568290588427</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.621053625456197</v>
+        <v>-4.635398527261218</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.111896256906824</v>
+        <v>1.106158296184816</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7629806279910049</v>
+        <v>-0.9096581612720354</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.502885754608448</v>
+        <v>2.414879234639829</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.421804995551388</v>
+        <v>-4.436149897356409</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.207489891670571</v>
+        <v>1.201751930948563</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7629806279910049</v>
+        <v>-0.9096581612720354</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.518779937410271</v>
+        <v>2.430773417441653</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.262289892032018</v>
+        <v>-4.276634793837039</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.272441777518621</v>
+        <v>1.266703816796612</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6034655244716349</v>
+        <v>-0.7501430577526654</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.615634843962195</v>
+        <v>2.527628323993576</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.117617746932281</v>
+        <v>-4.131962648737302</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.340398738119956</v>
+        <v>1.334660777397947</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4587933793718975</v>
+        <v>-0.6054709126529281</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.712526233583477</v>
+        <v>2.624519713614859</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.099848288001325</v>
+        <v>-4.114193189806346</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26284621377906</v>
+        <v>1.257108253057051</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.441023920440942</v>
+        <v>-0.5877014537219725</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.638527601028772</v>
+        <v>2.550521081060154</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.013048790222316</v>
+        <v>-4.027393692027337</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.31996650621323</v>
+        <v>1.314228545491221</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.441023920440942</v>
+        <v>-0.5877014537219725</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.660928094351338</v>
+        <v>2.57292157438272</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.913356175493304</v>
+        <v>-3.927701077298325</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359915953478246</v>
+        <v>1.354177992756238</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3413313057119302</v>
+        <v>-0.4880088389929607</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.720816064562158</v>
+        <v>2.632809544593539</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.981726361817314</v>
+        <v>-3.996071263622335</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.343574801423344</v>
+        <v>1.337836840701336</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3320556066757153</v>
+        <v>-0.4787331399567458</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.737388406458588</v>
+        <v>2.64938188648997</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.860309932190837</v>
+        <v>-3.874654833995858</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.382578081905826</v>
+        <v>1.376840121183818</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3320556066757153</v>
+        <v>-0.4787331399567458</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.72782511509048</v>
+        <v>2.639818595121861</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7323400503571</v>
+        <v>3.770250942450875</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.063699736886408</v>
+        <v>2.934313061739505</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.860309932190837</v>
+        <v>-3.974913709789338</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.382578081905826</v>
+        <v>1.343991153510023</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3320556066757153</v>
+        <v>-0.4787331399567458</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.056763533872776</v>
+        <v>2.647073177765458</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240418.xlsx
+++ b/tame_output/ON/bt/strategyON_20240418.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>137.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-57.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.7%</t>
+          <t>788.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-559.1%</t>
+          <t>-569.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-241.8%</t>
+          <t>-246.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-332.5%</t>
+          <t>-317.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.3%</t>
+          <t>-161.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.9%</t>
+          <t>-271.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-191.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.3%</t>
+          <t>-180.8%</t>
         </is>
       </c>
     </row>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.283500627543588</v>
+        <v>-4.415833259019598</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.423981971232197</v>
+        <v>1.371048918641793</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.8659163920100523</v>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.715306420693375</v>
+        <v>-4.635631843135317</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.237592541439686</v>
+        <v>1.26946237246291</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.002333888451319</v>
+        <v>-0.8539890790988927</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.522671200959993</v>
+        <v>2.611678086571449</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.041738949561119</v>
+        <v>-4.962064372003061</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.09530430489468</v>
+        <v>1.127174135917903</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.084802138958467</v>
+        <v>-0.9364573296060408</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.461475025657794</v>
+        <v>2.55048191126925</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.377401596791572</v>
+        <v>-5.297727019233514</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9596198376584639</v>
+        <v>0.991489668681687</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.084802138958467</v>
+        <v>-0.9364573296060408</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.460055617313759</v>
+        <v>2.549062502925215</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.741027841691885</v>
+        <v>-5.661353264133827</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8206568999325801</v>
+        <v>0.8525267309558031</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.183023775825593</v>
+        <v>-1.034678966473167</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.407610195427726</v>
+        <v>2.496617081039182</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.106155224330632</v>
+        <v>-6.026480646772574</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6738604618829127</v>
+        <v>0.7057302929061358</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.479334560124606</v>
+        <v>-1.330989750772179</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.229078239854149</v>
+        <v>2.318085125465605</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.514744001511311</v>
+        <v>-6.435069423953252</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5091864950253999</v>
+        <v>0.5410563260486239</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.739578527952858</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.982686517560501</v>
+        <v>2.071693403171957</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.927726485652404</v>
+        <v>-6.848051908094345</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3391789338404232</v>
+        <v>0.3710487648636467</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.739578527952858</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.977871950031962</v>
+        <v>2.066878835643418</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.344118359939402</v>
+        <v>-7.264443782381343</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1706162347345015</v>
+        <v>0.202486065757725</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.739578527952858</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.975866000640839</v>
+        <v>2.064872886252295</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.720795370469246</v>
+        <v>-7.641120792911187</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03020412119124272</v>
+        <v>0.06207395221446621</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.739578527952858</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.986124691309518</v>
+        <v>2.075131576920974</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.066670192454055</v>
+        <v>-7.986995614895996</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1120462424569855</v>
+        <v>-0.08017641143376197</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.739578527952858</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.982224256455214</v>
+        <v>2.07123114206667</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.379494991699033</v>
+        <v>-8.299820414140974</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2387712420999759</v>
+        <v>-0.2069014110767524</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.739578527952858</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.980629176510215</v>
+        <v>2.069636062121671</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.676156333509232</v>
+        <v>-8.596481755951173</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.353656802894847</v>
+        <v>-0.3217869718716235</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.808321663686736</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.943162270999096</v>
+        <v>2.032169156610552</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.109505441619467</v>
+        <v>-9.029830864061408</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.531022750673344</v>
+        <v>-0.4991529196501205</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.808321663686736</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.939135966464693</v>
+        <v>2.028142852076148</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.492506830362098</v>
+        <v>-9.412832252804039</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6843254074919809</v>
+        <v>-0.652455576468757</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.808321663686736</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.939033865143108</v>
+        <v>2.028040750754564</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.867492156533375</v>
+        <v>-9.787817578975316</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8317480219890614</v>
+        <v>-0.7998781909658379</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.183306989858014</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.716614185411772</v>
+        <v>1.805621071023228</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.22702247903738</v>
+        <v>-10.14734790147932</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9702098476926118</v>
+        <v>-0.9383400166693887</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.183306989858014</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.721964488709822</v>
+        <v>1.810971374321278</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.55342250770239</v>
+        <v>-10.47374793014433</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.092853839201439</v>
+        <v>-1.060984008178216</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.658051827875453</v>
+        <v>-2.509707018523027</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.534040491467992</v>
+        <v>1.623047377079448</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.77257147577659</v>
+        <v>-10.69289689821853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.17747167580935</v>
+        <v>-1.145601844786126</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.728855986597224</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.405592861245242</v>
+        <v>1.494599746856698</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.76888055082018</v>
+        <v>-10.68920597326212</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.175995305826785</v>
+        <v>-1.144125474803562</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.728855986597224</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.405592861245242</v>
+        <v>1.494599746856698</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.97313872615004</v>
+        <v>-10.89346414859198</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.252185378840089</v>
+        <v>-1.220315547816865</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.00483974056364</v>
+        <v>-2.856494931211213</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.334522691595491</v>
+        <v>1.423529577206947</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.19117649778122</v>
+        <v>-11.11150192022316</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.334917933008124</v>
+        <v>-1.3030481019849</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.179610508659539</v>
+        <v>-3.031265699307112</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.234142785222388</v>
+        <v>1.323149670833844</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.11770666611377</v>
+        <v>-11.03803208855571</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.290158298847722</v>
+        <v>-1.258288467824499</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.10614067699209</v>
+        <v>-2.957795867639664</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.293596385716278</v>
+        <v>1.382603271327734</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.29283108350031</v>
+        <v>-11.21315650594225</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.345652845054824</v>
+        <v>-1.3137830140316</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.281265094378634</v>
+        <v>-3.132920285026207</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.203076956031869</v>
+        <v>1.292083841643325</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.5272831775148</v>
+        <v>-11.44760859995674</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.446652847562215</v>
+        <v>-1.414783016538992</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.281265094378634</v>
+        <v>-3.132920285026207</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.195857791130273</v>
+        <v>1.284864676741729</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.81508702205204</v>
+        <v>-11.73541244449398</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.568446576151087</v>
+        <v>-1.536576745127863</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.569068938915872</v>
+        <v>-3.420724129563446</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.016503293633954</v>
+        <v>1.105510179245409</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.04491146921587</v>
+        <v>-11.96523689165781</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.659260565178061</v>
+        <v>-1.627390734154837</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.731716475986033</v>
+        <v>-3.583371666633606</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9200305612304134</v>
+        <v>1.009037446841869</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.27694038895213</v>
+        <v>-12.19726581139407</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.749378404443451</v>
+        <v>-1.717508573420227</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.645384363822029</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8855166715464744</v>
+        <v>0.9745235571579305</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.22492487498331</v>
+        <v>-12.14525029742525</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.724581863169525</v>
+        <v>-1.692712032146301</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.645384363822029</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8895070072328752</v>
+        <v>0.9785138928443313</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.36659671670743</v>
+        <v>-12.28692213914938</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.782725826757915</v>
+        <v>-1.750855995734691</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.645384363822029</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8880317803341335</v>
+        <v>0.9770386659455896</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.46550345716671</v>
+        <v>-12.38582887960865</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.807235112776752</v>
+        <v>-1.775365281753529</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.892635913633731</v>
+        <v>-3.744291104281305</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8437411462234405</v>
+        <v>0.9327480318348966</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.26635134992961</v>
+        <v>-12.18667677237155</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.740625403528596</v>
+        <v>-1.708755572505372</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.727313387683918</v>
+        <v>-3.578968578331491</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9298835281466458</v>
+        <v>1.018890413758101</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.0405061972102</v>
+        <v>-11.96083161965214</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.640708269404623</v>
+        <v>-1.608838438381399</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.537041902744328</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9646186065351525</v>
+        <v>1.053625492146609</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.7542313848875</v>
+        <v>-11.67455680732945</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.525059199919486</v>
+        <v>-1.493189368896262</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.537041902744328</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9657577510912114</v>
+        <v>1.054764636702668</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.80712667293179</v>
+        <v>-11.72745209537373</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.543583540975092</v>
+        <v>-1.511713709951869</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.532086556655881</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9713647329063866</v>
+        <v>1.060371618517843</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.52321794200304</v>
+        <v>-11.44354336444498</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.424286344364956</v>
+        <v>-1.392416513341733</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.532086556655881</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9770984371450231</v>
+        <v>1.066105322756479</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.27623069181009</v>
+        <v>-11.19655611425203</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.335228706681641</v>
+        <v>-1.303358875658417</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.285099306462929</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.115553524866929</v>
+        <v>1.204560410478385</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.01239382460602</v>
+        <v>-10.93271924704796</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.239577441112921</v>
+        <v>-1.207707610089697</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.285099306462929</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.105670043554022</v>
+        <v>1.194676929165478</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.74515202373762</v>
+        <v>-10.66547744617956</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.134515281264935</v>
+        <v>-1.102645450241712</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.285099306462929</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.103835483054648</v>
+        <v>1.192842368666104</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.46934286033714</v>
+        <v>-10.38966828277908</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.024491930878202</v>
+        <v>-0.9926220998549788</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.344424807536623</v>
+        <v>-3.196079998184196</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156946753048427</v>
+        <v>1.245953638659883</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.44538931936118</v>
+        <v>-10.36571474180312</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.014242008342325</v>
+        <v>-0.9823721773191019</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.320471266560665</v>
+        <v>-3.172126457208238</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171987383779495</v>
+        <v>1.260994269390951</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.18132938103838</v>
+        <v>-10.10165480348032</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9218783491749587</v>
+        <v>-0.8900085181517348</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.908066518885442</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.317163030611421</v>
+        <v>1.406169916222877</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.474249757533546</v>
+        <v>-9.394575179975487</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6418335334333247</v>
+        <v>-0.6099637024101012</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.908066518885442</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.31437599695112</v>
+        <v>1.403382882562576</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.434065459167355</v>
+        <v>-9.354390881609296</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6254161901990072</v>
+        <v>-0.5935463591757837</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.016227029871678</v>
+        <v>-2.867882220519252</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338830199858676</v>
+        <v>1.427837085470132</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.353995663629551</v>
+        <v>-9.274321086071492</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5940214507631283</v>
+        <v>-0.5621516197399048</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.936157234333874</v>
+        <v>-2.787812424981448</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.386238898402115</v>
+        <v>1.475245784013571</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.120514441399951</v>
+        <v>-9.040839863841892</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4927045330334363</v>
+        <v>-0.4608347020102128</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.702676012104276</v>
+        <v>-2.554331202751849</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.534252060577727</v>
+        <v>1.623258946189183</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.940805911256078</v>
+        <v>-8.861131333698019</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4237133312888459</v>
+        <v>-0.3918435002656224</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64550450794158</v>
+        <v>-2.497159698589153</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.565662752762385</v>
+        <v>1.654669638373841</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.808530437625191</v>
+        <v>-8.728855860067132</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.375435655089464</v>
+        <v>-0.3435658240662405</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.513229034310693</v>
+        <v>-2.364884224958267</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.640395523687944</v>
+        <v>1.7294024092994</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.617930762952037</v>
+        <v>-8.538256185393978</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.296380724532566</v>
+        <v>-0.2645108935093425</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.174284550285114</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.757570389179472</v>
+        <v>1.846577274790928</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.368930964268456</v>
+        <v>-8.289256386710397</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1838744638354748</v>
+        <v>-0.1520046328122513</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.174284550285114</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.770476730403131</v>
+        <v>1.859483616014587</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.47452095404156</v>
+        <v>-8.394846376483502</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3540863893439354</v>
+        <v>-0.3222165583207115</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.279874540058219</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.579146806940049</v>
+        <v>1.668153692551505</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.493255856160157</v>
+        <v>-8.413581278602098</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3130360083142878</v>
+        <v>-0.2811661772910643</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.279874540058219</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.627691148817136</v>
+        <v>1.716698034428592</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.345315814752558</v>
+        <v>-8.265641237194499</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3737389144394156</v>
+        <v>-0.3418690834161922</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.407898433502087</v>
+        <v>-2.259553624149661</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.520004775674103</v>
+        <v>1.609011661285559</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.218423408317488</v>
+        <v>-8.138748830759429</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3316959381188656</v>
+        <v>-0.2998261070956421</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.132661217714591</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.587426233281667</v>
+        <v>1.676433118893123</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.174875001546797</v>
+        <v>-8.095200423988738</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3212371875056821</v>
+        <v>-0.2893673564824586</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.132661217714591</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.580465621186574</v>
+        <v>1.669472506798029</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.932726608092938</v>
+        <v>-7.853052030534879</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2099154757429957</v>
+        <v>-0.1780456447197722</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.132661217714591</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.594927975567717</v>
+        <v>1.683934861179172</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.86949723632459</v>
+        <v>-7.789822658766531</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1900916065764617</v>
+        <v>-0.1582217755532378</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.281006027067018</v>
+        <v>-2.132661217714591</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.589460096026912</v>
+        <v>1.678466981638367</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.683009543947584</v>
+        <v>-7.603334966389525</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1179984356150823</v>
+        <v>-0.08612860459185878</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.094518334690011</v>
+        <v>-1.946173525337585</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.698850805463692</v>
+        <v>1.787857691075148</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.661860345044141</v>
+        <v>-7.582185767486082</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1018377778163799</v>
+        <v>-0.06996794679315599</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.073369135786568</v>
+        <v>-1.925024326434141</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.719241303043084</v>
+        <v>1.808248188654539</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.418094903060696</v>
+        <v>-7.338420325502637</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.008550892675951438</v>
+        <v>0.02331893834727206</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.073369135786568</v>
+        <v>-1.925024326434141</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.715022011390134</v>
+        <v>1.80402889700159</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.154066835867436</v>
+        <v>-7.074392258309377</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09918464812136873</v>
+        <v>0.1310544791445922</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.723158927618188</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.838265564599722</v>
+        <v>1.927272450211178</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.904216441918361</v>
+        <v>-6.824541864360302</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1918668806847008</v>
+        <v>0.2237367117079243</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.723158927618188</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.831007639583424</v>
+        <v>1.920014525194881</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.600648952914383</v>
+        <v>-6.520974375356324</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.316892999806941</v>
+        <v>0.3487628308301645</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.871503736970614</v>
+        <v>-1.723158927618188</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.834606763104073</v>
+        <v>1.923613648715529</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.527169044062369</v>
+        <v>-6.44749446650431</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3596124694023004</v>
+        <v>0.3914823004255239</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.7980238281186</v>
+        <v>-1.649679018766173</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.892022214469836</v>
+        <v>1.981029100081291</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.302136044393546</v>
+        <v>-6.222461466835487</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4486461468861265</v>
+        <v>0.48051597790935</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.572990828449777</v>
+        <v>-1.42464601909735</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.026062491887426</v>
+        <v>2.115069377498882</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.087501666757139</v>
+        <v>-6.109180072847829</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5391946989950065</v>
+        <v>0.5305233365587303</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.35835645081337</v>
+        <v>-1.311364625109693</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.159537919523587</v>
+        <v>2.187733014945794</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.820901309782787</v>
+        <v>-5.842579715873478</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6270291005685431</v>
+        <v>0.6183577381322669</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.35835645081337</v>
+        <v>-1.311364625109693</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.140732178307383</v>
+        <v>2.16892727372959</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.580470812977927</v>
+        <v>-5.602149219068617</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7249443759153644</v>
+        <v>0.7162730134790882</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.11792595400851</v>
+        <v>-1.070934128304832</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.286733553015177</v>
+        <v>2.314928648437383</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.337680005328481</v>
+        <v>-5.359358411419172</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8259900128099629</v>
+        <v>0.8173186503736867</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.11792595400851</v>
+        <v>-1.070934128304832</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.290662866849997</v>
+        <v>2.318857962272204</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.098074913721392</v>
+        <v>-5.119753319812082</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9225106333701385</v>
+        <v>0.9138392709338627</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.050878006340016</v>
+        <v>-1.003886180636338</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.331570219368434</v>
+        <v>2.35976531479064</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.855419325298229</v>
+        <v>-4.877097731388918</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.016570939959397</v>
+        <v>1.007899577523121</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.050878006340016</v>
+        <v>-1.003886180636338</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.328568290588427</v>
+        <v>2.356763386010634</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.635398527261218</v>
+        <v>-4.657076933351908</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.106158296184816</v>
+        <v>1.09748693374854</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9096581612720354</v>
+        <v>-0.8626663355683577</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.414879234639829</v>
+        <v>2.443074330062036</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.436149897356409</v>
+        <v>-4.457828303447099</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.201751930948563</v>
+        <v>1.193080568512287</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9096581612720354</v>
+        <v>-0.8626663355683577</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.430773417441653</v>
+        <v>2.458968512863859</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.276634793837039</v>
+        <v>-4.298313199927729</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.266703816796612</v>
+        <v>1.258032454360337</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7501430577526654</v>
+        <v>-0.7031512320489878</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.527628323993576</v>
+        <v>2.555823419415783</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.131962648737302</v>
+        <v>-4.153641054827991</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.334660777397947</v>
+        <v>1.325989414961672</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6054709126529281</v>
+        <v>-0.5584790869492503</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.624519713614859</v>
+        <v>2.652714809037065</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.114193189806346</v>
+        <v>-4.135871595897036</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.257108253057051</v>
+        <v>1.248436890620775</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5877014537219725</v>
+        <v>-0.5407096280182947</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.550521081060154</v>
+        <v>2.57871617648236</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.027393692027337</v>
+        <v>-4.049072098118026</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.314228545491221</v>
+        <v>1.305557183054945</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5877014537219725</v>
+        <v>-0.5407096280182947</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.57292157438272</v>
+        <v>2.601116669804926</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.927701077298325</v>
+        <v>-3.949379483389015</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.354177992756238</v>
+        <v>1.345506630319962</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4880088389929607</v>
+        <v>-0.4410170132892829</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.632809544593539</v>
+        <v>2.661004640015746</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.996071263622335</v>
+        <v>-4.017749669713025</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.337836840701336</v>
+        <v>1.32916547826506</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.431741314253068</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.64938188648997</v>
+        <v>2.677576981912177</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.874654833995858</v>
+        <v>-3.896333240086548</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.376840121183818</v>
+        <v>1.368168758747542</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.431741314253068</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.639818595121861</v>
+        <v>2.668013690544068</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.770250942450875</v>
+        <v>3.815126086813516</v>
       </c>
       <c r="C1938" t="n">
         <v>2.934313061739505</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.974913709789338</v>
+        <v>-4.08004562173593</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.343991153510023</v>
+        <v>1.301938388731386</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4787331399567458</v>
+        <v>-0.4697336745482243</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.647073177765458</v>
+        <v>2.652472857010571</v>
       </c>
     </row>
   </sheetData>
